--- a/task202/golden/claims_annex.xlsx
+++ b/task202/golden/claims_annex.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Payments and holds'!$6:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Payments and holds'!$A$1:$F$19</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Payments and holds'!$A$1:$H$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -469,15 +469,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -490,7 +492,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>The check held PHP 1,355,297 back over the eighteen closed claim months, and PHP 5,091,404 of what partners claimed had not been settled when the archive was cut.</t>
+          <t>The check held PHP 1,331,518 back over the eighteen closed claim months, and PHP 5,002,074 of what partners claimed had not been settled when the archive was cut.</t>
         </is>
       </c>
     </row>
@@ -521,22 +523,32 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
+          <t>Passed by the check</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
           <t>Held by the check</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Recovered in the runs</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>Not settled in the archive</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>Transferred by the runs</t>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Settled by the Treasury</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Payment instructions</t>
         </is>
       </c>
     </row>
@@ -547,19 +559,25 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>32629209</v>
+        <v>32056732</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>267012</v>
+        <v>31794406</v>
       </c>
       <c r="D7" s="6" t="n">
+        <v>262327</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="6" t="n">
-        <v>226694</v>
-      </c>
       <c r="F7" s="6" t="n">
-        <v>32135504</v>
+        <v>222717</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>31571689</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>486</v>
       </c>
     </row>
     <row r="8">
@@ -569,19 +587,25 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>31769423</v>
+        <v>31212030</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>147874</v>
+        <v>31066751</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2370</v>
+        <v>145280</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>863467</v>
+        <v>2328</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>30755712</v>
+        <v>848317</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>30216105</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>483</v>
       </c>
     </row>
     <row r="9">
@@ -591,19 +615,25 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>25194008</v>
+        <v>24751981</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>270559</v>
+        <v>24486170</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1231</v>
+        <v>265812</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>537140</v>
+        <v>1210</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>24385079</v>
+        <v>527715</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>23957244</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>493</v>
       </c>
     </row>
     <row r="10">
@@ -613,19 +643,25 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>28140223</v>
+        <v>27646505</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>165711</v>
+        <v>27483702</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>3552</v>
+        <v>162803</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>1216110</v>
+        <v>3489</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>26754851</v>
+        <v>1194773</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>26285439</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>481</v>
       </c>
     </row>
     <row r="11">
@@ -635,19 +671,25 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>41053381</v>
+        <v>40333102</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>275978</v>
+        <v>40061966</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4842</v>
+        <v>271136</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>1017440</v>
+        <v>4757</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>39755121</v>
+        <v>999589</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>39057620</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>488</v>
       </c>
     </row>
     <row r="12">
@@ -657,19 +699,25 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>40759836</v>
+        <v>40044708</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>228163</v>
+        <v>39820548</v>
       </c>
       <c r="D12" s="6" t="n">
+        <v>224160</v>
+      </c>
+      <c r="E12" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="6" t="n">
-        <v>1230553</v>
-      </c>
       <c r="F12" s="6" t="n">
-        <v>39301120</v>
+        <v>1208963</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>38611585</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>484</v>
       </c>
     </row>
     <row r="13">
@@ -679,44 +727,57 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>199546080</v>
+        <v>196045058</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>1355297</v>
+        <v>194713543</v>
       </c>
       <c r="D13" s="8" t="n">
-        <v>11995</v>
+        <v>1331518</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>5091404</v>
+        <v>11784</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>193087387</v>
+        <v>5002074</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>189699682</v>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>2915</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Claimed less held, recovered and not yet settled equals transferred in every quarter.</t>
+          <t>Claimed less held, recovered and not yet settled equals settled in every quarter, and claimed less held equals passed.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Each side is keyed to the claim month: the month a return was filed for, and for a payment run line the claim month it covers.</t>
+          <t>A payment instruction settles a partner's claim month. Where the first half's release was held for a mandate re-validation the Treasury settled both halves on one instruction, and the archive is an instruction extract, so that instruction's amounts stand on each of the two run lines it covers: those lines together come to more than the partner claimed for the month, which cannot be settled, so they are one instruction and one amount.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>The 39 partner claim-months with no run line in the extract were released in a run dated after the archive's cut-off of 31 January 2026 and are shown as not settled; the manifest records the cut-off.</t>
+          <t>Each side is keyed to the claim month: the month a return was filed for, and for a payment run line the claim month it covers.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>The 39 partner claim-months with no run line in the extract were released in a run dated after the archive's cut-off of 31 January 2026 and are shown as not settled; the manifest records the cut-off.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>A recovery is applied against the partner's next transfer, so it falls in the quarter after the one the negative claim line sits in.</t>
         </is>
